--- a/mmc_enrollment_vs_spending.xlsx
+++ b/mmc_enrollment_vs_spending.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/isaac/Documents/RProjects/s2p_data_analyses/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55996469-3D36-3241-AC36-7402428B3554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C3AD7A0-09F2-074A-ABF4-D8A3AF411366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table" sheetId="4" r:id="rId1"/>
@@ -1143,6 +1143,31 @@
   </cellStyles>
   <dxfs count="6">
     <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
     </dxf>
     <dxf>
@@ -1171,31 +1196,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="10" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -3368,16 +3368,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{66E7D33D-54A7-E54F-9360-7E4950789BDC}" name="Table1" displayName="Table1" ref="A1:G15" totalsRowShown="0" headerRowDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{66E7D33D-54A7-E54F-9360-7E4950789BDC}" name="Table1" displayName="Table1" ref="A1:G15" totalsRowShown="0" headerRowDxfId="0">
   <autoFilter ref="A1:G15" xr:uid="{66E7D33D-54A7-E54F-9360-7E4950789BDC}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{CF27716F-5074-3346-8523-72F1900144BD}" name="Data  Type"/>
     <tableColumn id="2" xr3:uid="{C96BD2F9-89B3-A14C-81FC-E3A8DFCC8429}" name="Fiscal Year"/>
-    <tableColumn id="3" xr3:uid="{01CACE81-45D7-7446-B728-9B2B83E78B79}" name="State Spending" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{06BEE8CE-98D5-CA4D-9416-5950D90F162E}" name="Average Annual Enrollment" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{3EADD39B-572C-DC49-936D-3495F631C368}" name="Average Annual Enrollment Change %" dataDxfId="2" dataCellStyle="Percent"/>
-    <tableColumn id="6" xr3:uid="{2153D761-E319-9740-9788-8F81F69BBF9E}" name="Average Annual Spending per Enrollee" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{009E49B7-E7EF-3B4A-845E-8634520B2845}" name="Average Annual Spending per Enrollee Annual Change %" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{01CACE81-45D7-7446-B728-9B2B83E78B79}" name="State Spending" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{06BEE8CE-98D5-CA4D-9416-5950D90F162E}" name="Average Annual Enrollment" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{3EADD39B-572C-DC49-936D-3495F631C368}" name="Average Annual Enrollment Change %" dataDxfId="3" dataCellStyle="Percent"/>
+    <tableColumn id="6" xr3:uid="{2153D761-E319-9740-9788-8F81F69BBF9E}" name="Average Annual Spending per Enrollee" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{009E49B7-E7EF-3B4A-845E-8634520B2845}" name="Average Annual Spending per Enrollee Annual Change %" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3764,34 +3764,34 @@
       <c r="B4" s="25"/>
       <c r="C4" s="28">
         <f t="shared" ref="C4:C7" si="0">D4*12</f>
-        <v>58054450.559618697</v>
+        <v>57965641.133994684</v>
       </c>
       <c r="D4" s="28">
         <f>(1+$G$28)*D5</f>
-        <v>4837870.879968225</v>
+        <v>4830470.0944995573</v>
       </c>
       <c r="E4" s="32" t="s">
         <v>63</v>
       </c>
       <c r="F4" s="28">
         <f>C4-C5</f>
-        <v>1032104.4643248171</v>
+        <v>1030525.5913223624</v>
       </c>
       <c r="G4" s="30">
         <f>F4/C5</f>
-        <v>1.8099999999999963E-2</v>
+        <v>1.8099999999999884E-2</v>
       </c>
       <c r="H4" s="34">
         <f>K4*D4</f>
-        <v>23107709208.880447</v>
+        <v>23072359940.003639</v>
       </c>
       <c r="I4" s="34">
         <f>H4-H5</f>
-        <v>730803557.59148788</v>
+        <v>729685602.92017365</v>
       </c>
       <c r="J4" s="31">
         <f>I4/H5</f>
-        <v>3.2658830000000111E-2</v>
+        <v>3.265883000000009E-2</v>
       </c>
       <c r="K4" s="29">
         <f>(1+M4)*K5</f>
@@ -3813,34 +3813,34 @@
       <c r="B5" s="25"/>
       <c r="C5" s="28">
         <f t="shared" si="0"/>
-        <v>57022346.09529388</v>
+        <v>56935115.542672321</v>
       </c>
       <c r="D5" s="28">
         <f>(1+$G$28)*D6</f>
-        <v>4751862.1746078236</v>
+        <v>4744592.9618893601</v>
       </c>
       <c r="E5" s="32" t="s">
         <v>63</v>
       </c>
       <c r="F5" s="28">
         <f>C5-C6</f>
-        <v>1013755.4899566025</v>
+        <v>1012204.6864967793</v>
       </c>
       <c r="G5" s="30">
         <f>F5/C6</f>
-        <v>1.809999999999996E-2</v>
+        <v>1.8100000000000036E-2</v>
       </c>
       <c r="H5" s="34">
         <f>K5*D5</f>
-        <v>22376905651.28896</v>
+        <v>22342674337.083466</v>
       </c>
       <c r="I5" s="34">
         <f>H5-H6</f>
-        <v>707691191.28287888</v>
+        <v>706608593.00469208</v>
       </c>
       <c r="J5" s="31">
         <f>I5/H6</f>
-        <v>3.265882999999993E-2</v>
+        <v>3.2658829999999993E-2</v>
       </c>
       <c r="K5" s="29">
         <f>(1+M5)*K6</f>
@@ -3862,34 +3862,34 @@
       <c r="B6" s="25"/>
       <c r="C6" s="28">
         <f t="shared" si="0"/>
-        <v>56008590.605337277</v>
+        <v>55922910.856175542</v>
       </c>
       <c r="D6" s="28">
         <f>(1+$G$28)*D7</f>
-        <v>4667382.5504447734</v>
+        <v>4660242.5713479621</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>63</v>
       </c>
       <c r="F6" s="28">
         <f>C6-C7</f>
-        <v>995732.72758726776</v>
+        <v>994209.494643718</v>
       </c>
       <c r="G6" s="30">
         <f>F6/C7</f>
-        <v>1.8099999999999866E-2</v>
+        <v>1.8099999999999856E-2</v>
       </c>
       <c r="H6" s="34">
         <f>K6*D6</f>
-        <v>21669214460.006081</v>
+        <v>21636065744.078773</v>
       </c>
       <c r="I6" s="34">
         <f>H6-H7</f>
-        <v>685309775.81712723</v>
+        <v>684261415.75208282</v>
       </c>
       <c r="J6" s="48">
         <f>I6/H7</f>
-        <v>3.2658829999999833E-2</v>
+        <v>3.2658829999999868E-2</v>
       </c>
       <c r="K6" s="29">
         <f>(1+M6)*K7</f>
@@ -3911,18 +3911,18 @@
       <c r="B7" s="27"/>
       <c r="C7" s="28">
         <f t="shared" si="0"/>
-        <v>55012857.877750009</v>
+        <v>54928701.361531824</v>
       </c>
       <c r="D7" s="28">
         <f>(1+$G$28)*D8</f>
-        <v>4584404.8231458338</v>
+        <v>4577391.780127652</v>
       </c>
       <c r="E7" s="32" t="s">
         <v>63</v>
       </c>
       <c r="F7" s="28">
         <f>C7-C8</f>
-        <v>1598961.8777500093</v>
+        <v>1680126.0888045505</v>
       </c>
       <c r="G7" s="30">
         <f>G28</f>
@@ -3930,15 +3930,15 @@
       </c>
       <c r="H7" s="34">
         <f>K7*D7</f>
-        <v>20983904684.188953</v>
+        <v>20951804328.326691</v>
       </c>
       <c r="I7" s="34">
         <f>H7-H8</f>
-        <v>663636194.16989136</v>
+        <v>662620989.50152206</v>
       </c>
       <c r="J7" s="48">
         <f>I7/H8</f>
-        <v>3.2658830000000104E-2</v>
+        <v>3.2658829999999923E-2</v>
       </c>
       <c r="K7" s="32">
         <f>(1+M7)*K8</f>
@@ -3960,35 +3960,35 @@
       <c r="B8" s="27"/>
       <c r="C8" s="28">
         <f>C9/(B9/12)</f>
-        <v>53413896</v>
+        <v>53248575.272727273</v>
       </c>
       <c r="D8" s="28">
         <f>((C8+C10)/2)/12</f>
-        <v>4502902.291666667</v>
+        <v>4496013.9280303037</v>
       </c>
       <c r="E8" s="28">
         <f>C8/12</f>
-        <v>4451158</v>
+        <v>4437381.2727272725</v>
       </c>
       <c r="F8" s="28">
         <f>C8-C10</f>
-        <v>-1241863</v>
+        <v>-1407183.7272727266</v>
       </c>
       <c r="G8" s="31">
         <f>(C8-C10)/C10</f>
-        <v>-2.2721539737468471E-2</v>
+        <v>-2.5746302915173616E-2</v>
       </c>
       <c r="H8" s="34">
         <f>K8*D8</f>
-        <v>20320268490.019062</v>
+        <v>20289183338.825169</v>
       </c>
       <c r="I8" s="49">
         <f>H8-H10</f>
-        <v>56268490.019062042</v>
+        <v>25183338.82516861</v>
       </c>
       <c r="J8" s="48">
         <f>I8/H10</f>
-        <v>2.7767711221408429E-3</v>
+        <v>1.2427624765677363E-3</v>
       </c>
       <c r="K8" s="32">
         <f>(1+M8)*K10</f>
@@ -4008,16 +4008,16 @@
         <v>69</v>
       </c>
       <c r="B9" s="27">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C9" s="28">
-        <v>31158106</v>
+        <v>48811194</v>
       </c>
       <c r="D9" s="28">
-        <v>4451158</v>
+        <v>4437381.2727272697</v>
       </c>
       <c r="E9" s="28">
-        <v>4419503</v>
+        <v>4442646</v>
       </c>
       <c r="F9" s="32" t="s">
         <v>63</v>
@@ -4637,7 +4637,7 @@
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" t="str">
         <f>_xlfn.CONCAT("(2) Full-year Enrollment 2026 Estimate Represents YTD annualized. Months in YTD = ",B9,".")</f>
-        <v>(2) Full-year Enrollment 2026 Estimate Represents YTD annualized. Months in YTD = 7.</v>
+        <v>(2) Full-year Enrollment 2026 Estimate Represents YTD annualized. Months in YTD = 11.</v>
       </c>
       <c r="G27" t="s">
         <v>37</v>
